--- a/artfynd/S 500-2026 artfynd.xlsx
+++ b/artfynd/S 500-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1425,10 +1425,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>861139</v>
+        <v>135365792</v>
       </c>
       <c r="B9" t="n">
-        <v>80433</v>
+        <v>80488</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1436,37 +1436,40 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hamra kronopark, Dlr</t>
+          <t>Kölsjöån, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>494098</v>
+        <v>481494</v>
       </c>
       <c r="R9" t="n">
-        <v>6843624</v>
+        <v>6844020</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1490,12 +1493,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2009-08-06</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2009-08-06</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1510,22 +1523,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Ulf Lindenbaum</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Via Ulf Lindenbaum</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2060599</v>
+        <v>135365761</v>
       </c>
       <c r="B10" t="n">
-        <v>80461</v>
+        <v>57972</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1533,37 +1546,49 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hamra kronopark, Dlr</t>
+          <t>Stendammen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>494098</v>
+        <v>481939</v>
       </c>
       <c r="R10" t="n">
-        <v>6843624</v>
+        <v>6844040</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1587,12 +1612,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2009-08-06</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2009-08-06</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1607,22 +1642,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Ulf Lindenbaum</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Via Ulf Lindenbaum</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>112181503</v>
+        <v>861139</v>
       </c>
       <c r="B11" t="n">
-        <v>90932</v>
+        <v>80433</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1630,41 +1665,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1962</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Tandsjöborg, Dlr</t>
+          <t>Hamra kronopark, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478467</v>
+        <v>494098</v>
       </c>
       <c r="R11" t="n">
-        <v>6837144</v>
+        <v>6843624</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1688,17 +1719,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-07-11</t>
+          <t>2009-08-06</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-07-11</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2009-08-06</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1713,64 +1739,60 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Via Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>112182455</v>
+        <v>2060599</v>
       </c>
       <c r="B12" t="n">
-        <v>79084</v>
+        <v>80461</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>6462</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Tandsjöborg, Dlr</t>
+          <t>Hamra kronopark, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478404</v>
+        <v>494098</v>
       </c>
       <c r="R12" t="n">
-        <v>6836834</v>
+        <v>6843624</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1794,17 +1816,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-07-11</t>
+          <t>2009-08-06</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-07-11</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2009-08-06</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1819,44 +1836,44 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Via Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>112182726</v>
+        <v>112181503</v>
       </c>
       <c r="B13" t="n">
-        <v>97989</v>
+        <v>90932</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221941</v>
+        <v>1962</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1870,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478455</v>
+        <v>478467</v>
       </c>
       <c r="R13" t="n">
-        <v>6836985</v>
+        <v>6837144</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1937,10 +1954,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>112181861</v>
+        <v>112182455</v>
       </c>
       <c r="B14" t="n">
-        <v>79917</v>
+        <v>79084</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1948,21 +1965,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1976,10 +1993,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478401</v>
+        <v>478404</v>
       </c>
       <c r="R14" t="n">
-        <v>6836829</v>
+        <v>6836834</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2040,6 +2057,218 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>112182726</v>
+      </c>
+      <c r="B15" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Tandsjöborg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>478455</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6836985</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2023-07-11</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2023-07-11</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>112181861</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Tandsjöborg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>478401</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6836829</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2023-07-11</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2023-07-11</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/S 500-2026 artfynd.xlsx
+++ b/artfynd/S 500-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Hälsinglands flora (2019)</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83984925</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
           <t>Hälsinglands flora (2019)</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83984916</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
           <t>Hälsinglands flora (2019)</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83984910</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1112,6 +1132,11 @@
           <t>Hälsinglands flora (2019)</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83984917</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1209,6 +1234,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133680613</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1325,6 +1355,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134556382</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1422,6 +1457,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128943480</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1532,6 +1572,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135365792</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1651,6 +1696,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135365761</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1748,6 +1798,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/861139</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1845,6 +1900,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2060599</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1951,6 +2011,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112181503</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2057,6 +2122,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112182455</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2163,6 +2233,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112182726</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2269,8 +2344,30 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112181861</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/S 500-2026 artfynd.xlsx
+++ b/artfynd/S 500-2026 artfynd.xlsx
@@ -1468,7 +1468,7 @@
         <v>135365792</v>
       </c>
       <c r="B9" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>135365761</v>
       </c>
       <c r="B10" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/S 500-2026 artfynd.xlsx
+++ b/artfynd/S 500-2026 artfynd.xlsx
@@ -1468,7 +1468,7 @@
         <v>135365792</v>
       </c>
       <c r="B9" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/S 500-2026 artfynd.xlsx
+++ b/artfynd/S 500-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ14"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1465,10 +1465,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>861139</v>
+        <v>135365792</v>
       </c>
       <c r="B9" t="n">
-        <v>80433</v>
+        <v>80556</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1476,37 +1476,40 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hamra kronopark, Dlr</t>
+          <t>Kölsjöån, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>494098</v>
+        <v>481494</v>
       </c>
       <c r="R9" t="n">
-        <v>6843624</v>
+        <v>6844020</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1530,12 +1533,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2009-08-06</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2009-08-06</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1550,27 +1563,27 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Ulf Lindenbaum</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Via Ulf Lindenbaum</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/861139</t>
+          <t>https://artportalen.se/Sighting/135365792</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2060599</v>
+        <v>135365761</v>
       </c>
       <c r="B10" t="n">
-        <v>80461</v>
+        <v>57977</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1578,37 +1591,49 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hamra kronopark, Dlr</t>
+          <t>Stendammen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>494098</v>
+        <v>481939</v>
       </c>
       <c r="R10" t="n">
-        <v>6843624</v>
+        <v>6844040</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1632,12 +1657,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2009-08-06</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2009-08-06</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1652,27 +1687,27 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Ulf Lindenbaum</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Via Ulf Lindenbaum</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/2060599</t>
+          <t>https://artportalen.se/Sighting/135365761</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>112181503</v>
+        <v>861139</v>
       </c>
       <c r="B11" t="n">
-        <v>90932</v>
+        <v>80433</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1680,41 +1715,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1962</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Tandsjöborg, Dlr</t>
+          <t>Hamra kronopark, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478467</v>
+        <v>494098</v>
       </c>
       <c r="R11" t="n">
-        <v>6837144</v>
+        <v>6843624</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1738,17 +1769,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-07-11</t>
+          <t>2009-08-06</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-07-11</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2009-08-06</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1763,69 +1789,65 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Via Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112181503</t>
+          <t>https://artportalen.se/Sighting/861139</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>112182455</v>
+        <v>2060599</v>
       </c>
       <c r="B12" t="n">
-        <v>79084</v>
+        <v>80461</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>6462</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Tandsjöborg, Dlr</t>
+          <t>Hamra kronopark, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478404</v>
+        <v>494098</v>
       </c>
       <c r="R12" t="n">
-        <v>6836834</v>
+        <v>6843624</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1849,17 +1871,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-07-11</t>
+          <t>2009-08-06</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-07-11</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2009-08-06</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1874,49 +1891,49 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Via Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112182455</t>
+          <t>https://artportalen.se/Sighting/2060599</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>112182726</v>
+        <v>112181503</v>
       </c>
       <c r="B13" t="n">
-        <v>97989</v>
+        <v>90932</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221941</v>
+        <v>1962</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1930,10 +1947,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478455</v>
+        <v>478467</v>
       </c>
       <c r="R13" t="n">
-        <v>6836985</v>
+        <v>6837144</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1996,16 +2013,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112182726</t>
+          <t>https://artportalen.se/Sighting/112181503</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>112181861</v>
+        <v>112182455</v>
       </c>
       <c r="B14" t="n">
-        <v>79917</v>
+        <v>79084</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2013,21 +2030,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2041,10 +2058,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478401</v>
+        <v>478404</v>
       </c>
       <c r="R14" t="n">
-        <v>6836829</v>
+        <v>6836834</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2106,6 +2123,228 @@
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112182455</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>112182726</v>
+      </c>
+      <c r="B15" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Tandsjöborg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>478455</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6836985</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2023-07-11</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2023-07-11</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112182726</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>112181861</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Tandsjöborg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>478401</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6836829</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2023-07-11</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2023-07-11</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/112181861</t>
         </is>
@@ -2126,6 +2365,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
